--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/araucania.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/araucania.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>23341.21</v>
+        <v>23424.51</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>13883.56</v>
+        <v>13929.23</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>12272.64</v>
+        <v>12484.49</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>8607.84</v>
+        <v>8589.209999999999</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>15146.42</v>
+        <v>14971.12</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>9070.530000000001</v>
+        <v>9111.629999999999</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>13910.57</v>
+        <v>13928.4</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>21393.57</v>
+        <v>21656.5</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>57567.96</v>
+        <v>59279.05</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>10490.71</v>
+        <v>10532.07</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>7133.58</v>
+        <v>7221.37</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>14930.82</v>
+        <v>15114.58</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>27741.91</v>
+        <v>27919.34</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>6493.13</v>
+        <v>6534.66</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>9262.639999999999</v>
+        <v>9239.26</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>7457.34</v>
+        <v>7528.19</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>7498.34</v>
+        <v>7569.58</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>9852.889999999999</v>
+        <v>9926.299999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>13616.04</v>
+        <v>13580.03</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>153194.57</v>
+        <v>150046.15</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>11364.08</v>
+        <v>11408.32</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>7770.35</v>
+        <v>7730.99</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>23091.21</v>
+        <v>22822.53</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/araucania.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/araucania.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,37 +514,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3935-239-CM25</t>
+          <t>3502-103-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.190.900-K</t>
+          <t>69.180.700-2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRE</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>OFISILLAS CHILE SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>76.855.435-8</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,28 +569,28 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>23424.51</v>
+        <v>5608.04</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1175-2616-CM25</t>
+          <t>1187104-26-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>COMERCIAL FENIX LTDA</t>
+          <t>PEDRO ANTONIO PEDREROS CONCHA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.029.126-9</t>
+          <t>10.595.925-7</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,28 +630,28 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>13929.23</v>
+        <v>7030.33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3290-337-CM25</t>
+          <t>1187104-28-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.607.400-8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>SERVICIO DE SALUD ARAUCANIA SUR</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,28 +691,28 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>12484.49</v>
+        <v>7284.59</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1057780-122-CM25</t>
+          <t>1187104-83-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.955.100-1</t>
+          <t>61.607.400-8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE</t>
+          <t>SERVICIO DE SALUD ARAUCANIA SUR</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>IBARRA BARRIOS ESTERILIZACIÓN LIMITADA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.577.724-0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>8589.209999999999</v>
+        <v>16835.02</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1057780-120-CM25</t>
+          <t>3935-239-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,27 +768,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.955.100-1</t>
+          <t>69.190.900-K</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE</t>
+          <t>I MUNICIPALIDAD DE FREIRE</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS MEDICOS Y DEPORTIVOS PTM CHILE SPA</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>77.749.210-1</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>14971.12</v>
+        <v>23424.51</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1968-3290-CM25</t>
+          <t>1175-2616-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.004.087-K</t>
+          <t>61.607.400-8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>SERVICIO DE SALUD ARAUCANIA SUR</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>COMERCIAL FENIX LTDA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>76.029.126-9</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>9111.629999999999</v>
+        <v>13929.23</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1968-3314-CM25</t>
+          <t>3290-337-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.004.087-K</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ENILDA TERESA FIGUEROA MELLADO</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>6.189.318-0</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>13928.4</v>
+        <v>12484.49</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3608-767-CM25</t>
+          <t>1057780-122-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,22 +956,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.190.600-0</t>
+          <t>61.955.100-1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAAVEDRA</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CHILESEATING</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.675.854-1</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>21656.5</v>
+        <v>8589.209999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5586-358-CM26</t>
+          <t>1057780-120-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,27 +1012,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>61.955.100-1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>INDUMAC LTDA.</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS MEDICOS Y DEPORTIVOS PTM CHILE SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>83.732.700-8</t>
+          <t>77.749.210-1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>59279.05</v>
+        <v>14971.12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4114-24-CM26</t>
+          <t>1968-3290-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,27 +1073,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.181.000-3</t>
+          <t>61.004.087-K</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURACAUTIN</t>
+          <t>Dirección Regional de Gendarmeria - Temuco</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>10532.07</v>
+        <v>9111.629999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2548-210-CM26</t>
+          <t>1968-3314-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>61.004.087-K</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>Dirección Regional de Gendarmeria - Temuco</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>ENILDA TERESA FIGUEROA MELLADO</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>6.189.318-0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>7221.37</v>
+        <v>13928.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1175-299-CM26</t>
+          <t>3608-767-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,27 +1195,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.607.400-8</t>
+          <t>69.190.600-0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA SUR</t>
+          <t>I MUNICIPALIDAD DE SAAVEDRA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
+          <t>CHILESEATING</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>15.888.842-4</t>
+          <t>76.675.854-1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>15114.58</v>
+        <v>21656.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1057780-40-CM26</t>
+          <t>5586-358-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.955.100-1</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>INDUMAC LTDA.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>83.732.700-8</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>27919.34</v>
+        <v>59279.05</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3751-115-CM26</t>
+          <t>4114-24-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.191.300-7</t>
+          <t>69.181.000-3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
+          <t>I MUNICIPALIDAD DE CURACAUTIN</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>6534.66</v>
+        <v>10532.07</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1426099-86-CM26</t>
+          <t>1175-299-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.607.400-8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SERVICIO DE SALUD ARAUCANIA SUR</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>ENILDA TERESA FIGUEROA MELLADO</t>
+          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>6.189.318-0</t>
+          <t>15.888.842-4</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>9239.26</v>
+        <v>15114.58</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2179-102-CM26</t>
+          <t>2548-210-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>7528.19</v>
+        <v>7221.37</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3708-167-CM26</t>
+          <t>1057780-40-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.191.300-7</t>
+          <t>61.955.100-1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>7569.58</v>
+        <v>27919.34</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4281-100-CM26</t>
+          <t>3751-115-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,27 +1561,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.191.000-8</t>
+          <t>69.191.300-7</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CUNCO</t>
+          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>9926.299999999999</v>
+        <v>6534.66</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1175-521-CM26</t>
+          <t>1426099-86-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,12 +1622,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.607.400-8</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA SUR</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>ENILDA TERESA FIGUEROA MELLADO</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
+          <t>6.189.318-0</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>13580.03</v>
+        <v>9239.26</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5586-1964-CM26</t>
+          <t>2179-102-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,27 +1683,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>INDUMAC LTDA.</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>83.732.700-8</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>150046.15</v>
+        <v>7528.19</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2548-373-CM26</t>
+          <t>3708-167-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>69.191.300-7</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>11408.32</v>
+        <v>7569.58</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2548-379-CM26</t>
+          <t>4281-100-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>69.191.000-8</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>I MUNICIPALIDAD DE CUNCO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ENILDA TERESA FIGUEROA MELLADO</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>6.189.318-0</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>7730.99</v>
+        <v>9926.299999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3434-68-CM26</t>
+          <t>1175-521-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,27 +1866,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>61.607.400-8</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - IX Zona Araucania</t>
+          <t>SERVICIO DE SALUD ARAUCANIA SUR</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>LOYDA EUGENIA HENRÍQUEZ ORELLANA</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>11.216.890-7</t>
+          <t>78.874.470-6</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,6 +1911,250 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
+        <v>13580.03</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>5586-1964-CM26</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>87.912.900-1</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>INDUMAC LTDA.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>83.732.700-8</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>150046.15</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2548-373-CM26</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>61.955.000-5</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>11408.32</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2548-379-CM26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>61.955.000-5</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ENILDA TERESA FIGUEROA MELLADO</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>6.189.318-0</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>7730.99</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>3434-68-CM26</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>60.505.522-2</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Carabineros de Chile - IX Zona Araucania</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>LOYDA EUGENIA HENRÍQUEZ ORELLANA</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>11.216.890-7</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
         <v>22822.53</v>
       </c>
     </row>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/araucania.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/araucania.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Araucanía" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Araucanía" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3502-103-CM25</t>
+          <t>986278-1-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>feb-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-02-12</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.180.700-2</t>
+          <t>65.148.017-5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE LA ARAUCANIA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>OFISILLAS CHILE SPA</t>
+          <t>MUEBLES ANDROMEDA DOS SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.855.435-8</t>
+          <t>77.285.439-0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>5608.04</v>
+        <v>91234.92</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1187104-26-CM25</t>
+          <t>3502-103-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>may-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.607.400-8</t>
+          <t>69.180.700-2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA SUR</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO PEDREROS CONCHA</t>
+          <t>OFISILLAS CHILE SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10.595.925-7</t>
+          <t>76.855.435-8</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>7030.33</v>
+        <v>5608.04</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1187104-28-CM25</t>
+          <t>2387-129-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +646,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>may-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.607.400-8</t>
+          <t>69.191.600-6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA SUR</t>
+          <t>I MUNICIPALIDAD DE PUCON</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>7284.59</v>
+        <v>5894.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1187104-83-CM25</t>
+          <t>655-21-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>jun-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.607.400-8</t>
+          <t>61.821.000-6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA SUR</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION IX REGION</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>IBARRA BARRIOS ESTERILIZACIÓN LIMITADA</t>
+          <t>COMERCIALIZADORA MERCADO PUBLICO SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.577.724-0</t>
+          <t>76.559.762-5</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,43 +752,43 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>16835.02</v>
+        <v>6221.06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3935-239-CM25</t>
+          <t>2179-117-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.190.900-K</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRE</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,28 +813,28 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>23424.51</v>
+        <v>11093.49</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1175-2616-CM25</t>
+          <t>1187104-27-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>COMERCIAL FENIX LTDA</t>
+          <t>IBARRA BARRIOS ESTERILIZACIÓN LIMITADA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.029.126-9</t>
+          <t>76.577.724-0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,28 +874,28 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>13929.23</v>
+        <v>10075.18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3290-337-CM25</t>
+          <t>1187104-26-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.607.400-8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>SERVICIO DE SALUD ARAUCANIA SUR</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>PEDRO ANTONIO PEDREROS CONCHA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>10.595.925-7</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,28 +935,28 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>12484.49</v>
+        <v>7030.33</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1057780-122-CM25</t>
+          <t>1187104-25-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.955.100-1</t>
+          <t>61.607.400-8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE</t>
+          <t>SERVICIO DE SALUD ARAUCANIA SUR</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,28 +996,28 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>8589.209999999999</v>
+        <v>8414.219999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1057780-120-CM25</t>
+          <t>1187104-28-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.955.100-1</t>
+          <t>61.607.400-8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE</t>
+          <t>SERVICIO DE SALUD ARAUCANIA SUR</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS MEDICOS Y DEPORTIVOS PTM CHILE SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>77.749.210-1</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,43 +1057,43 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>14971.12</v>
+        <v>7284.59</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1968-3290-CM25</t>
+          <t>1187104-83-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.004.087-K</t>
+          <t>61.607.400-8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>SERVICIO DE SALUD ARAUCANIA SUR</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>IBARRA BARRIOS ESTERILIZACIÓN LIMITADA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>76.577.724-0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,28 +1118,28 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>9111.629999999999</v>
+        <v>16835.02</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1968-3314-CM25</t>
+          <t>1175-1890-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.004.087-K</t>
+          <t>61.607.400-8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>SERVICIO DE SALUD ARAUCANIA SUR</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ENILDA TERESA FIGUEROA MELLADO</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>6.189.318-0</t>
+          <t>78.874.470-6</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,43 +1179,43 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>13928.4</v>
+        <v>28997.42</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3608-767-CM25</t>
+          <t>1426099-143-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.190.600-0</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAAVEDRA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CHILESEATING</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.675.854-1</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,28 +1240,28 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>21656.5</v>
+        <v>16066.94</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5586-358-CM26</t>
+          <t>1658-3851-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>69.190.700-7</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>INDUMAC LTDA.</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>83.732.700-8</t>
+          <t>77.599.784-2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,28 +1301,28 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>59279.05</v>
+        <v>20720.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4114-24-CM26</t>
+          <t>1057780-48-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.181.000-3</t>
+          <t>61.955.100-1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURACAUTIN</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>77.599.784-2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,28 +1362,28 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>10532.07</v>
+        <v>7887.84</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1175-299-CM26</t>
+          <t>1057780-50-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.607.400-8</t>
+          <t>61.955.100-1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA SUR</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>15.888.842-4</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,28 +1423,28 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>15114.58</v>
+        <v>5796.98</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2548-210-CM26</t>
+          <t>3710-610-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>69.180.900-5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>I MUNICIPALIDAD DE VICTORIA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>INDUSTRIA DE CAMAS Y TEXTILES LIMITADA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>76.404.809-1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,43 +1484,43 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>7221.37</v>
+        <v>16249.79</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1057780-40-CM26</t>
+          <t>765-342-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.955.100-1</t>
+          <t>72.396.000-2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE</t>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>PEDRO ANTONIO PEDREROS CONCHA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>10.595.925-7</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,43 +1545,43 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>27919.34</v>
+        <v>9577.59</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3751-115-CM26</t>
+          <t>4322-400-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.191.300-7</t>
+          <t>69.190.300-1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
+          <t>I MUNICIPALIDAD DE PERQUENCO</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>6534.66</v>
+        <v>7047.01</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1426099-86-CM26</t>
+          <t>3935-239-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,27 +1622,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.190.900-K</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE FREIRE</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ENILDA TERESA FIGUEROA MELLADO</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>6.189.318-0</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>9239.26</v>
+        <v>23424.51</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2179-102-CM26</t>
+          <t>1175-2616-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.607.400-8</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SERVICIO DE SALUD ARAUCANIA SUR</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>COMERCIAL FENIX LTDA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.029.126-9</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>7528.19</v>
+        <v>13929.23</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3708-167-CM26</t>
+          <t>3290-337-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,27 +1744,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.191.300-7</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>7569.58</v>
+        <v>12484.49</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>4281-100-CM26</t>
+          <t>1057780-122-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,27 +1805,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.191.000-8</t>
+          <t>61.955.100-1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CUNCO</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>9926.299999999999</v>
+        <v>8589.209999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1175-521-CM26</t>
+          <t>1057780-120-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.607.400-8</t>
+          <t>61.955.100-1</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA SUR</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS MEDICOS Y DEPORTIVOS PTM CHILE SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
+          <t>77.749.210-1</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>13580.03</v>
+        <v>14971.12</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5586-1964-CM26</t>
+          <t>1968-3290-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>61.004.087-K</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>Dirección Regional de Gendarmeria - Temuco</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>INDUMAC LTDA.</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>83.732.700-8</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>150046.15</v>
+        <v>9111.629999999999</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2548-373-CM26</t>
+          <t>1968-3314-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,27 +1988,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>61.004.087-K</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>Dirección Regional de Gendarmeria - Temuco</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>ENILDA TERESA FIGUEROA MELLADO</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>6.189.318-0</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>11408.32</v>
+        <v>13928.4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2548-379-CM26</t>
+          <t>3608-767-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>69.190.600-0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>I MUNICIPALIDAD DE SAAVEDRA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>ENILDA TERESA FIGUEROA MELLADO</t>
+          <t>CHILESEATING</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>6.189.318-0</t>
+          <t>76.675.854-1</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>7730.99</v>
+        <v>21656.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3434-68-CM26</t>
+          <t>5586-358-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - IX Zona Araucania</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>LOYDA EUGENIA HENRÍQUEZ ORELLANA</t>
+          <t>INDUMAC LTDA.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>11.216.890-7</t>
+          <t>83.732.700-8</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,6 +2155,860 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
+        <v>59279.05</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>4114-24-CM26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>69.181.000-3</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CURACAUTIN</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>STATUS SPA</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>77.393.671-4</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>10532.07</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1175-299-CM26</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>61.607.400-8</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARAUCANIA SUR</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>15.888.842-4</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>15114.58</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2548-210-CM26</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>61.955.000-5</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>STATUS SPA</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>77.393.671-4</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>7221.37</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>1057780-40-CM26</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>61.955.100-1</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>DROGUERIA HOFMANN SAC</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>27919.34</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>3751-115-CM26</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>69.191.300-7</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>6534.66</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1426099-86-CM26</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ENILDA TERESA FIGUEROA MELLADO</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>6.189.318-0</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>9239.26</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2179-102-CM26</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>60.301.001-9</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>7528.19</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>3708-167-CM26</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>69.191.300-7</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>LEFI SPA</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>7569.58</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>4281-100-CM26</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>69.191.000-8</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CUNCO</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>9926.299999999999</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>1175-521-CM26</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>61.607.400-8</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARAUCANIA SUR</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>78.874.470-6</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>13580.03</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>5586-1964-CM26</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>87.912.900-1</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>INDUMAC LTDA.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>83.732.700-8</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>150046.15</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2548-373-CM26</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>61.955.000-5</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>11408.32</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2548-379-CM26</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>61.955.000-5</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ENILDA TERESA FIGUEROA MELLADO</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>6.189.318-0</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>7730.99</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>3434-68-CM26</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>60.505.522-2</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Carabineros de Chile - IX Zona Araucania</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>LOYDA EUGENIA HENRÍQUEZ ORELLANA</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>11.216.890-7</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="n">
         <v>22822.53</v>
       </c>
     </row>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/araucania.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/araucania.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -534,7 +534,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1307,7 +1307,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1057780-48-CM25</t>
+          <t>1057780-50-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>7887.84</v>
+        <v>5796.98</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1057780-50-CM25</t>
+          <t>1057780-48-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>77.599.784-2</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>5796.98</v>
+        <v>7887.84</v>
       </c>
     </row>
     <row r="17">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2222,7 +2222,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1175-299-CM26</t>
+          <t>2548-210-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.607.400-8</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA SUR</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>15.888.842-4</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>15114.58</v>
+        <v>7221.37</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2548-210-CM26</t>
+          <t>1175-299-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>61.607.400-8</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>SERVICIO DE SALUD ARAUCANIA SUR</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>15.888.842-4</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>7221.37</v>
+        <v>15114.58</v>
       </c>
     </row>
     <row r="32">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - IX Zona Araucania</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3010,6 +3010,128 @@
       </c>
       <c r="M42" s="2" t="n">
         <v>22822.53</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>1968-2232-CM26</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>61.004.087-K</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ENILDA TERESA FIGUEROA MELLADO</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>6.189.318-0</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>13293.25</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>5586-3380-CM26</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>87.912.900-1</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ENILDA TERESA FIGUEROA MELLADO</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>6.189.318-0</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>7852.16</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/araucania.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/araucania.xlsx
@@ -562,7 +562,11 @@
           <t>77.285.439-0</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>76.855.435-8</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +753,11 @@
           <t>76.559.762-5</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +818,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1005,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1192,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1318,11 @@
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1444,11 @@
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1631,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1696,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1822,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1887,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2013,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2261,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2326,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2391,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2456,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2521,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2647,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2712,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2777,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2842,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2968,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/araucania.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/araucania.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1335,7 +1335,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1057780-50-CM25</t>
+          <t>1057780-48-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1375,28 +1375,32 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>77.599.784-2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>5796.98</v>
+        <v>7887.84</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1057780-48-CM25</t>
+          <t>1057780-50-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1436,26 +1440,22 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>7887.84</v>
+        <v>5796.98</v>
       </c>
     </row>
     <row r="17">
@@ -2278,7 +2278,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2548-210-CM26</t>
+          <t>1175-299-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>61.607.400-8</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>SERVICIO DE SALUD ARAUCANIA SUR</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2318,12 +2318,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>15.888.842-4</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2337,13 +2337,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>7221.37</v>
+        <v>15114.58</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1175-299-CM26</t>
+          <t>2548-210-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2368,12 +2368,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.607.400-8</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA SUR</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2383,12 +2383,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>15.888.842-4</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2402,7 +2402,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>15114.58</v>
+        <v>7221.37</v>
       </c>
     </row>
     <row r="32">
@@ -2599,7 +2599,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2179-102-CM26</t>
+          <t>3708-167-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2619,17 +2619,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>69.191.300-7</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2658,13 +2658,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>7528.19</v>
+        <v>7569.58</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3708-167-CM26</t>
+          <t>2179-102-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2684,17 +2684,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.191.300-7</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>7569.58</v>
+        <v>7528.19</v>
       </c>
     </row>
     <row r="37">
@@ -3224,6 +3224,136 @@
       </c>
       <c r="M44" s="2" t="n">
         <v>7852.16</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>1175-939-CM26</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>61.607.400-8</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARAUCANIA SUR</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>MUEBLES CAMILA GALLEGUILLOS E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>77.043.435-1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>21831.11</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>5066-247-CM26</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>69.191.300-7</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>12184.8</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/araucania.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/araucania.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/araucania.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/araucania.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2599,7 +2599,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3708-167-CM26</t>
+          <t>2179-102-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2619,17 +2619,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.191.300-7</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2658,13 +2658,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>7569.58</v>
+        <v>7528.19</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2179-102-CM26</t>
+          <t>3708-167-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2684,17 +2684,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>69.191.300-7</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>7528.19</v>
+        <v>7569.58</v>
       </c>
     </row>
     <row r="37">
@@ -3354,6 +3354,71 @@
       </c>
       <c r="M46" s="2" t="n">
         <v>12184.8</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>3495-303-CM26</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>69.190.800-3</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>12646.02</v>
       </c>
     </row>
   </sheetData>
